--- a/Outputs/Scenarios/PtX_demand_IE_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_IE_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>1.495982210596268e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001941480072570625</v>
+        <v>0.002111915457780947</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0004359684784121134</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.003882960145141249</v>
+        <v>0.003487747827296907</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>1.198882933440846e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>0.002690274328038775</v>
+        <v>0.002690274328038774</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>7.256840918350278e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0.02631342574369097</v>
+        <v>0.02631342574369096</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>2.15545713815099e-07</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0006471600241902082</v>
+        <v>0.0004359684784121134</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>2.214619532340416e-05</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01047643320777818</v>
+        <v>0.01139612069498154</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.002352532333094571</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.02095286641555635</v>
+        <v>0.01882025866475657</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>1.165589227547588e-06</v>
       </c>
       <c r="K42" t="n">
-        <v>0.003492144402592726</v>
+        <v>0.002352532333094571</v>
       </c>
     </row>
     <row r="43">
